--- a/intermediate_data/approved_vs_unapproved_drugs_LR_ttest.xlsx
+++ b/intermediate_data/approved_vs_unapproved_drugs_LR_ttest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7976510067114093</v>
+        <v>0.8194949494949494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6537837837837838</v>
+        <v>0.6840677966101696</v>
       </c>
       <c r="E2" t="n">
-        <v>57.25212388866793</v>
+        <v>56.55828643339231</v>
       </c>
       <c r="F2" t="n">
-        <v>1.077082718760257e-77</v>
+        <v>3.476087715282468e-77</v>
       </c>
     </row>
     <row r="3">
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7921597633136095</v>
+        <v>0.7646884272997032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6682934131736527</v>
+        <v>0.655</v>
       </c>
       <c r="E3" t="n">
-        <v>54.19257655424843</v>
+        <v>40.31260208137765</v>
       </c>
       <c r="F3" t="n">
-        <v>2.095322054591587e-75</v>
+        <v>3.087683081436881e-63</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8035534591194969</v>
+        <v>0.7835534591194968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6662341772151898</v>
+        <v>0.6775632911392405</v>
       </c>
       <c r="E4" t="n">
-        <v>48.16252249195298</v>
+        <v>37.78423593864895</v>
       </c>
       <c r="F4" t="n">
-        <v>1.61877160927443e-70</v>
+        <v>1.276868220456329e-60</v>
       </c>
     </row>
     <row r="5">
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8357894736842105</v>
+        <v>0.8215181518151813</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6723509933774833</v>
+        <v>0.6488741721854305</v>
       </c>
       <c r="E5" t="n">
-        <v>56.00546724360395</v>
+        <v>76.29482982059386</v>
       </c>
       <c r="F5" t="n">
-        <v>8.927586431863989e-77</v>
+        <v>9.140958577538734e-90</v>
       </c>
     </row>
     <row r="6">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8221172638436484</v>
+        <v>0.7898039215686273</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6715131578947369</v>
+        <v>0.700032894736842</v>
       </c>
       <c r="E6" t="n">
-        <v>57.38953307338122</v>
+        <v>34.2497461148628</v>
       </c>
       <c r="F6" t="n">
-        <v>8.553938211723761e-78</v>
+        <v>1.074794133797175e-56</v>
       </c>
     </row>
     <row r="7">
@@ -575,16 +575,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7883333333333333</v>
+        <v>0.7910408921933086</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6675</v>
+        <v>0.6504868913857679</v>
       </c>
       <c r="E7" t="n">
-        <v>50.44217345157476</v>
+        <v>53.24715411213362</v>
       </c>
       <c r="F7" t="n">
-        <v>1.985738366128032e-72</v>
+        <v>1.130042090175558e-74</v>
       </c>
     </row>
     <row r="8">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8019713261648747</v>
+        <v>0.813440860215054</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6923826714801443</v>
+        <v>0.6810507246376812</v>
       </c>
       <c r="E8" t="n">
-        <v>34.59448651425884</v>
+        <v>47.04854499816709</v>
       </c>
       <c r="F8" t="n">
-        <v>4.301286413271009e-57</v>
+        <v>1.491491356632576e-69</v>
       </c>
     </row>
     <row r="9">
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7863837638376384</v>
+        <v>0.792814814814815</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6675092936802974</v>
+        <v>0.6568283582089554</v>
       </c>
       <c r="E9" t="n">
-        <v>39.68425982770198</v>
+        <v>41.7326321385006</v>
       </c>
       <c r="F9" t="n">
-        <v>1.336874038120472e-62</v>
+        <v>1.21085202381954e-64</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7990873015873017</v>
+        <v>0.7740079365079363</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6696000000000001</v>
+        <v>0.67476</v>
       </c>
       <c r="E10" t="n">
-        <v>46.95795110510979</v>
+        <v>32.03181968269983</v>
       </c>
       <c r="F10" t="n">
-        <v>1.790484239076255e-69</v>
+        <v>4.718347936679655e-54</v>
       </c>
     </row>
     <row r="11">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8159915611814346</v>
+        <v>0.772194092827004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6732340425531913</v>
+        <v>0.6737872340425531</v>
       </c>
       <c r="E11" t="n">
-        <v>49.34822833838984</v>
+        <v>35.98108873886316</v>
       </c>
       <c r="F11" t="n">
-        <v>1.602943539713558e-71</v>
+        <v>1.167360511507687e-58</v>
       </c>
     </row>
     <row r="12">
@@ -685,16 +685,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7963478260869564</v>
+        <v>0.8102608695652174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.683711790393013</v>
+        <v>0.695877192982456</v>
       </c>
       <c r="E12" t="n">
-        <v>34.34941615926717</v>
+        <v>39.19980904526761</v>
       </c>
       <c r="F12" t="n">
-        <v>8.241167181442985e-57</v>
+        <v>4.196659365452125e-62</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7936725663716815</v>
+        <v>0.7961946902654867</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6826222222222222</v>
+        <v>0.6825892857142857</v>
       </c>
       <c r="E13" t="n">
-        <v>29.63195184724972</v>
+        <v>32.99557286124649</v>
       </c>
       <c r="F13" t="n">
-        <v>5.113820796666065e-51</v>
+        <v>3.216257075796861e-55</v>
       </c>
     </row>
     <row r="14">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8171753246753248</v>
+        <v>0.8172638436482086</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6660784313725492</v>
+        <v>0.662</v>
       </c>
       <c r="E14" t="n">
-        <v>56.45950512022706</v>
+        <v>54.8525147192838</v>
       </c>
       <c r="F14" t="n">
-        <v>4.111605538678142e-77</v>
+        <v>6.56812028576903e-76</v>
       </c>
     </row>
     <row r="15">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7586124401913874</v>
+        <v>0.7909615384615383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6521256038647344</v>
+        <v>0.6516990291262136</v>
       </c>
       <c r="E15" t="n">
-        <v>32.06150317539144</v>
+        <v>38.88546673502638</v>
       </c>
       <c r="F15" t="n">
-        <v>4.339425343142577e-54</v>
+        <v>8.874984402730023e-62</v>
       </c>
     </row>
     <row r="16">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7953603603603604</v>
+        <v>0.8069683257918551</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6633636363636363</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>40.46189076354156</v>
+        <v>55.39399748928744</v>
       </c>
       <c r="F16" t="n">
-        <v>2.186291689025224e-63</v>
+        <v>2.56027080152504e-76</v>
       </c>
     </row>
     <row r="17">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.8180542986425339</v>
+        <v>0.825</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7045</v>
+        <v>0.6924657534246574</v>
       </c>
       <c r="E17" t="n">
-        <v>34.94685819393498</v>
+        <v>40.52992085754131</v>
       </c>
       <c r="F17" t="n">
-        <v>1.700313513073342e-57</v>
+        <v>1.868748678417221e-63</v>
       </c>
     </row>
     <row r="18">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8124170616113744</v>
+        <v>0.8215714285714286</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6715714285714287</v>
+        <v>0.6775119617224883</v>
       </c>
       <c r="E18" t="n">
-        <v>42.83397450052478</v>
+        <v>43.62560821758973</v>
       </c>
       <c r="F18" t="n">
-        <v>1.050361343765427e-65</v>
+        <v>1.875878346467286e-66</v>
       </c>
     </row>
     <row r="19">
@@ -839,16 +839,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8011574074074074</v>
+        <v>0.8062499999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6781944444444443</v>
+        <v>0.7017209302325582</v>
       </c>
       <c r="E19" t="n">
-        <v>36.4911732228004</v>
+        <v>31.37953679783048</v>
       </c>
       <c r="F19" t="n">
-        <v>3.191413113899622e-59</v>
+        <v>3.018769599215702e-53</v>
       </c>
     </row>
     <row r="20">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7863902439024391</v>
+        <v>0.7920098039215686</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6520588235294119</v>
+        <v>0.6611330049261082</v>
       </c>
       <c r="E20" t="n">
-        <v>37.76131167871832</v>
+        <v>36.58615568023254</v>
       </c>
       <c r="F20" t="n">
-        <v>1.350714159761607e-60</v>
+        <v>2.511055078709048e-59</v>
       </c>
     </row>
     <row r="21">
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.7641237113402062</v>
+        <v>0.7496391752577319</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6595336787564766</v>
+        <v>0.6821874999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>30.3033668998867</v>
+        <v>20.26948317027524</v>
       </c>
       <c r="F21" t="n">
-        <v>6.920477152567794e-52</v>
+        <v>5.180062679746528e-37</v>
       </c>
     </row>
     <row r="22">
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7872115384615386</v>
+        <v>0.7768749999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6714975845410628</v>
+        <v>0.6862621359223301</v>
       </c>
       <c r="E22" t="n">
-        <v>35.11603520532761</v>
+        <v>28.20261611368058</v>
       </c>
       <c r="F22" t="n">
-        <v>1.09204202059568e-57</v>
+        <v>4.086798890245283e-49</v>
       </c>
     </row>
     <row r="23">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7770930232558141</v>
+        <v>0.7744444444444442</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6767058823529412</v>
+        <v>0.6871764705882353</v>
       </c>
       <c r="E23" t="n">
-        <v>25.60269178590533</v>
+        <v>26.15694713480006</v>
       </c>
       <c r="F23" t="n">
-        <v>1.874103420062296e-45</v>
+        <v>2.94702034586319e-46</v>
       </c>
     </row>
     <row r="24">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7845454545454544</v>
+        <v>0.8012626262626261</v>
       </c>
       <c r="D24" t="n">
-        <v>0.642295918367347</v>
+        <v>0.655204081632653</v>
       </c>
       <c r="E24" t="n">
-        <v>42.38752786315834</v>
+        <v>45.84393994743729</v>
       </c>
       <c r="F24" t="n">
-        <v>2.810308801409412e-65</v>
+        <v>1.739094091004479e-68</v>
       </c>
     </row>
     <row r="25">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.826923076923077</v>
+        <v>0.8422222222222221</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7301932367149759</v>
+        <v>0.6967475728155341</v>
       </c>
       <c r="E25" t="n">
-        <v>31.99805921570868</v>
+        <v>43.96474712608542</v>
       </c>
       <c r="F25" t="n">
-        <v>5.190093870705139e-54</v>
+        <v>9.045649624883586e-67</v>
       </c>
     </row>
     <row r="26">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7816842105263159</v>
+        <v>0.7888359788359787</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6388829787234043</v>
+        <v>0.617872340425532</v>
       </c>
       <c r="E26" t="n">
-        <v>41.81105512142407</v>
+        <v>52.27556204822261</v>
       </c>
       <c r="F26" t="n">
-        <v>1.015459165139693e-64</v>
+        <v>6.575674982900103e-74</v>
       </c>
     </row>
     <row r="27">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.8403743315508022</v>
+        <v>0.8137433155080216</v>
       </c>
       <c r="D27" t="n">
-        <v>0.659193548387097</v>
+        <v>0.687135135135135</v>
       </c>
       <c r="E27" t="n">
-        <v>57.63249520468869</v>
+        <v>44.06052836602617</v>
       </c>
       <c r="F27" t="n">
-        <v>5.698417391381172e-78</v>
+        <v>7.368467725549007e-67</v>
       </c>
     </row>
     <row r="28">
@@ -1037,16 +1037,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7992134831460673</v>
+        <v>0.8091011235955056</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6766666666666667</v>
+        <v>0.6586931818181818</v>
       </c>
       <c r="E28" t="n">
-        <v>36.126118164982</v>
+        <v>54.57415318255487</v>
       </c>
       <c r="F28" t="n">
-        <v>8.060675863507218e-59</v>
+        <v>1.069675266538521e-75</v>
       </c>
     </row>
     <row r="29">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.8280459770114942</v>
+        <v>0.8033333333333335</v>
       </c>
       <c r="D29" t="n">
-        <v>0.656878612716763</v>
+        <v>0.673546511627907</v>
       </c>
       <c r="E29" t="n">
-        <v>50.81878613977678</v>
+        <v>41.62722721052562</v>
       </c>
       <c r="F29" t="n">
-        <v>9.769618865211743e-73</v>
+        <v>1.53468006407315e-64</v>
       </c>
     </row>
     <row r="30">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.787696629213483</v>
+        <v>0.8006779661016948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6554802259887005</v>
+        <v>0.6149152542372881</v>
       </c>
       <c r="E30" t="n">
-        <v>34.75095048632575</v>
+        <v>54.85728836271949</v>
       </c>
       <c r="F30" t="n">
-        <v>2.845733548888364e-57</v>
+        <v>6.51354662133901e-76</v>
       </c>
     </row>
     <row r="31">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8237560975609755</v>
+        <v>0.8125980392156862</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6644117647058825</v>
+        <v>0.6807881773399014</v>
       </c>
       <c r="E31" t="n">
-        <v>54.46781878718097</v>
+        <v>37.81415240013151</v>
       </c>
       <c r="F31" t="n">
-        <v>1.289528863086861e-75</v>
+        <v>1.186589489982596e-60</v>
       </c>
     </row>
   </sheetData>
